--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -471,11 +471,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -512,7 +512,7 @@
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="23" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -839,10 +839,8 @@
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>9768922502</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>9768922502</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -881,10 +879,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -922,19 +918,17 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>00:00 hour</t>
+          <t>00:52 hour</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>00:00 hour / 00:00 hour</t>
+          <t>23:08 hour / 00:00 hour</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr"/>
@@ -948,25 +942,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>CDB314</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="2" t="inlineStr">
@@ -1049,7 +1039,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -1062,10 +1052,8 @@
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>9851316119</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>9851316119</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -1092,7 +1080,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -1100,10 +1088,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>27.67154</t>
-        </is>
+      <c r="Y3" s="2" t="n">
+        <v>27.67154</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1112,7 +1098,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>Layer 1-User</t>
+          <t>Layer 1-</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -1156,43 +1142,39 @@
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>85.33876</t>
-        </is>
+      <c r="AP3" s="2" t="n">
+        <v>85.33875999999999</v>
       </c>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="2" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>11h 11m</t>
+          <t>12h 46m</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="AV3" s="2" t="inlineStr">
@@ -1214,7 +1196,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 9:24 AM</t>
+          <t>15 Sep 2026 10:55 AM</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1240,7 +1222,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1250,32 +1232,32 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>None</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9851322004</t>
+          <t>9825986033</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1286,24 +1268,24 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9851322004</t>
+          <t>BKT9825986033</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:38:08 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -1311,11 +1293,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1328,7 +1306,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>Laxman Koirala</t>
+          <t>L1  Support</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1339,12 +1317,12 @@
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+          <t>Kageshwori Manohara Municipality Ward No.7 office - Local government office P92M+XX3 Kageshwori Mano</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>workcgnet@gmail.com</t>
+          <t>test@test.com</t>
         </is>
       </c>
       <c r="AG4" s="2" t="inlineStr">
@@ -1353,17 +1331,21 @@
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>07:31 hour</t>
+        </is>
+      </c>
       <c r="AJ4" s="2" t="inlineStr"/>
       <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>Nisha Joshi</t>
+          <t>Kusum Gurung</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>Monali Lohani</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
@@ -1373,38 +1355,34 @@
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>L31-6</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
-      </c>
+          <t>L37-1</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="AS4" s="2" t="inlineStr">
         <is>
-          <t>1h 40m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="AT4" s="2" t="inlineStr">
         <is>
-          <t>1h 40m</t>
+          <t>21h 31m</t>
         </is>
       </c>
       <c r="AU4" s="2" t="inlineStr">
         <is>
-          <t>Other / In Progress (In Progress)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="AW4" s="2" t="inlineStr">
@@ -1421,7 +1399,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 8:51 AM</t>
+          <t>15 Sep 2026 9:24 AM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1447,7 +1425,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1457,17 +1435,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1477,12 +1455,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9841051986</t>
+          <t>9851322004</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1493,24 +1471,24 @@
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9841051986</t>
+          <t>9851322004</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 09:38:08 AM</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -1518,7 +1496,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1531,7 +1513,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>L1  Support</t>
+          <t>Laxman Koirala</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1542,31 +1524,31 @@
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr"/>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>02:54 hour</t>
-        </is>
-      </c>
+      <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr"/>
       <c r="AK5" s="2" t="inlineStr"/>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>Aakash Shah</t>
+          <t>Nisha Joshi</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Monali Lohani</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
@@ -1576,37 +1558,240 @@
       </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>L15-2</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr">
         <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 8:51 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>TKT1333787</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>9841051986</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>9841051986</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 05:06:15 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>L15-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="2" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT5" s="2" t="inlineStr">
+      <c r="AT6" s="2" t="inlineStr">
         <is>
           <t>15h 45m</t>
         </is>
       </c>
-      <c r="AU5" s="2" t="inlineStr">
+      <c r="AU6" s="2" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV5" s="2" t="inlineStr">
+      <c r="AV6" s="2" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1623,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1660,7 +1845,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1670,7 +1855,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1681,7 +1866,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1878,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>31m</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1890,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>13h 28m</t>
+          <t>16h 41m</t>
         </is>
       </c>
     </row>
@@ -1746,14 +1931,14 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1822,14 +2007,14 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1954,24 +2139,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:04:22 AM</t>
@@ -1984,82 +2169,149 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11h 11m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>TKT1333510</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Kabiraj Limbu</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:24:32 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>TKT1333787</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>15h 45m</t>
         </is>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -69,13 +72,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -95,17 +104,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -482,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -498,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -512,7 +524,7 @@
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -526,1272 +538,2378 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Target Employee</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Grid Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Grid User Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grid Employee Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grid Module</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grid Operation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grid IP Address</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grid Remark</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Case Origin</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Customer Name</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Mobile No</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sub Sub Category</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on SLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Estimated closed time based on TAT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>User Id</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Status</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Case Reason</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Assign Team</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Assign User</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Customer Address</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>Escalated Layer</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>SLA Left/Total</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>TAT Left/Total</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>Last Modified By</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Level</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Associated Location Name</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>Solution Given</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>Task / Issue Type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 9:35 AM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>fiber issue</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>TKT1334123</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Chaudhary</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="3" t="n">
         <v>9768922502</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:27:54 AM</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>17 Sep 2026 01: 26:00 PM</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>LTP9768922502</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:26:46 AM</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:35:50 AM</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>Layer 2-CG Group</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>Hari Rijal</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AD2" s="3" t="inlineStr"/>
+      <c r="AE2" s="3" t="inlineStr">
         <is>
           <t>Hyundai Service Kupondole - Hyundai dealer Kupondole Hts Rd Lalitpur 44600, Lalitpur, Nepal, Nepal</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AF2" s="3" t="inlineStr">
         <is>
           <t>chandramanitharu@gmail.com</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AG2" s="3" t="inlineStr">
         <is>
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n">
+      <c r="AH2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AI2" s="3" t="inlineStr">
         <is>
           <t>00:52 hour</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="3" t="inlineStr">
         <is>
           <t>23:08 hour / 00:00 hour</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr">
         <is>
           <t>Manisha kunwar</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AM2" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="n">
+      <c r="AN2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>CDB314</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="n">
+      <c r="AP2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AS2" s="3" t="inlineStr">
         <is>
           <t>7m</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AU2" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (In Progress)</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AV2" s="3" t="inlineStr">
         <is>
           <t>Case : fiber issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 9:04 AM</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>TKT1333983</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="3" t="n">
         <v>9851316119</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>9849181580</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>27.67154</v>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Layer 1-</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Balkumari, Indira Pharmacy nearby, 8, Bagmati, Central, Nepal</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>byanjankar.sudharna@gmail.com</t>
         </is>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>00:00 hour</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Nirajan Dhamala</t>
         </is>
       </c>
-      <c r="AM3" s="2" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="2" t="n">
+      <c r="AN3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AO3" s="2" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="n">
+      <c r="AP3" s="3" t="n">
         <v>85.33875999999999</v>
       </c>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="AS3" s="2" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>1h 35m</t>
         </is>
       </c>
-      <c r="AT3" s="2" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>12h 46m</t>
         </is>
       </c>
-      <c r="AU3" s="2" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV3" s="2" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55 AM</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>wifi 6</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>TKT1333510</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>9825986033</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="n">
+        <v>9825986033</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>BKT9825986033</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
         <is>
           <t>Kageshwori Manohara Municipality Ward No.7 office - Local government office P92M+XX3 Kageshwori Mano</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr">
+      <c r="AF4" s="3" t="inlineStr">
         <is>
           <t>test@test.com</t>
         </is>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
         <is>
           <t>07:31 hour</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr">
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>Kusum Gurung</t>
         </is>
       </c>
-      <c r="AM4" s="2" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L37-1</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 9:24 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>9851322004</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:38:08 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>27.71579</v>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="n">
+        <v>85.36396999999999</v>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1h 40m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 8:51 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333787</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>9841051986</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841051986</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 05:06:15 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L15-2</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>15h 45m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334079</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9818937555</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9818937555</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:17:25 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.736322</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Trijyoti Secondary School P9M6+RX4, Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>bdeschopnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>01:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>L37-1</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AS4" s="2" t="inlineStr">
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L19-4</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.363473</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>21h 31m</t>
-        </is>
-      </c>
-      <c r="AU4" s="2" t="inlineStr">
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV4" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 9:24 AM</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>wifi 6</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>TKT1334065</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Saradha Panta</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332693</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Saradha Panta</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9823402588</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:38:08 AM</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841501402</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 04:22:39 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.67367</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Bank 27.68204, 85.3491, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>11:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.35165</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>sky com to net tv</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333865</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:24:11 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>Laxman Koirala</t>
         </is>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>workcgnet@gmail.com</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr">
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Stupa Butcher Shop, M895+5M5, ?????????? ???, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>16h 18m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>16h 18m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334100</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9822474275</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CHB9822474275</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:05:49 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Gyaneswor, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>9766847818@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>Nisha Joshi</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>Monali Lohani</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr">
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>01:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>L31-6</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AS5" s="2" t="inlineStr">
-        <is>
-          <t>1h 40m</t>
-        </is>
-      </c>
-      <c r="AT5" s="2" t="inlineStr">
-        <is>
-          <t>1h 40m</t>
-        </is>
-      </c>
-      <c r="AU5" s="2" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV5" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h 17m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 8:51 AM</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>wifi 6</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>TKT1333787</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Ganesh bahadur dhakal</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334105</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Abhisesh Giri</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Ganesh bahadur dhakal</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>9841051986</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Abhisesh Giri</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9766847818</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>9841051986</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>CHB9766847818</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:09:34 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>Layer 1-User</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>L1  Support</t>
         </is>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>Dhakchin dhoka the luga ghar, Bagmati, Central, Nepal</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr">
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Gyaneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>Abhiseshgiri1234@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>02:54 hour</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>Aakash Shah</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="inlineStr">
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>01:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>L15-2</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AS6" s="2" t="inlineStr">
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="2" t="inlineStr">
-        <is>
-          <t>15h 45m</t>
-        </is>
-      </c>
-      <c r="AU6" s="2" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 8m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV6" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="2" t="inlineStr">
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1808,7 +2926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1827,493 +2945,831 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Total Audit Records Scraped</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>5</v>
+      <c r="B2" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Tickets Solved / Handled (Completed or MS Assigned)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>3</v>
+      <c r="B3" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Ticket Solution Rate</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Average Completion Time (From Assigned Date)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>31m</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>13m</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Average Completion Time (From Created Date)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>16h 41m</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>14h 20m</t>
         </is>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Overall Category Summary</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Category Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
+      <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="C17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>No Internet Connection</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TKT1333983</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Sudharna Byanjankar</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>1h 35m</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>12h 46m</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TKT1333510</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:24:32 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333787</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 05:06:15 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>21h 31m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TKT1333787</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Ganesh bahadur dhakal</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>15h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334079</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:17:25 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>15h 45m</t>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332693</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 04:22:39 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334100</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:05:49 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>2h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334105</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Abhisesh Giri</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:09:34 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:17:53 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,14 +494,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -523,12 +523,12 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
@@ -1959,10 +1959,8 @@
           <t>Bijaye Subedi</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9818937555</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9818937555</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1997,10 +1995,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.736322</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.736322</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2056,25 +2052,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L19-4</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.363473</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.363473</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2170,10 +2162,8 @@
           <t>Girish Ojha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9823402588</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9823402588</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2208,10 +2198,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.67367</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.67367</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2267,25 +2255,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.35165</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35165000000001</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2381,10 +2365,8 @@
           <t>Dolma Lama</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9818723103</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9818723103</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2466,10 +2448,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
@@ -2480,7 +2460,7 @@
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2576,10 +2556,8 @@
           <t>Abisesh Giri 1</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9822474275</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9822474275</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2669,10 +2647,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2659,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2779,10 +2755,8 @@
           <t>Abhisesh Giri</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9766847818</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9766847818</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2872,10 +2846,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -2886,32 +2858,3398 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 8m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV blank display</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334172</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9842097155</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9842097155</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:58:03 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.686495</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Active English Secondary School Active English Secondary School - High school M9JP+R53 Bhaktapur Roa</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>damakcadil@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>02:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.378118</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 8m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9844064169</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9844064169</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.66527</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali Bus Stop,Tikathali, Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>kurt.kushal1989@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>06:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB471</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3599</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:31 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333455</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana jimee</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana jimee</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9851150629</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9856022476</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 12:32:40 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.68817</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur,kathmandu,near Gurudwara Guru Nanak Satsang, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>Jimeeranjana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>10:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB506</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.31543</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu
+(15 Sep 2026 01:31:35 PM) :
+Router has been upgraded
+TKT1333455
+9856022476
+Ranjana jimee
+New SN : ALCLFE4FE240
+Old SN : ALCLB2B212F3
+Note : Upgrade to wifi6
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu
+(15 Sep 2026 01:31:35 PM) :
+Router has been upgraded
+TKT1333455
+9856022476
+Ranjana jimee
+New SN : ALCLFE4FE240
+Old SN : ALCLB2B212F3
+Note : Upgrade to wifi6
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333363</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851177792</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851177792</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 11:24:30 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.69393</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Ghostwriting Nepal, Bhadra Vinayak Marga , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>suneetaraut@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>11:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L47-2</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.331616</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Dual band</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334089</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Arun Bhandari</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Arun Bhandari</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9865297766</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9868297864</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:40:37 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.69864</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Near Puja Pratisthan ???? ??????????, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>arunbhandari698@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Parajuli</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L64-5</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.33317</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:21 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>for wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333526</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Uttam KC</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Uttam KC</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9865667017</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:36:58 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9865667017</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:34:08 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:21:58 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Corona Pre-School, P7GR+8MX, Dhungedhara Road, Nagarjun 44600 - Near Corona Pre-School, P7GR+8M</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>uttamkc71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>09:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:13 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333979</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>lavkush kumar mukhiya</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>lavkush kumar mukhiya</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9762420859</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>KLK9762420859</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:13:52 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>nar by Kumari Club Building - Club Dakchhinkali Road Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9851424302@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB022</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333912</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9869527479</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>KLK9869527479</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:56:46 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Lolang tarakeshwor , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L51-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 31m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334125</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Niran Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Niran Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9845603766</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9845603766</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:28:19 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.73941</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near nagaarjun party place, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB046</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.3076</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>3h 17m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:22 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334129</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Uday Bhahadur Rana Magar</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Uday Bhahadur Rana Magar</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9851070038</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:22:18 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9851070038</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:31:27 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:24:45 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.756502</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Dhalmal pul baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>raamagaruday18@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.317497</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1h 2m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332927</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 07:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.755555</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Rosemary Idol Boarding School - School Q846+3R, 8 Tarakeshwar 44610, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>aryalmadhukar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L41-8A</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.310901</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:45 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332927</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Madhukar Aryal</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860752387</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 07:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:51:53 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.755555</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Rosemary Idol Boarding School - School Q846+3R, 8 Tarakeshwar 44610, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>aryalmadhukar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L41-8A</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.310901</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 22m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:40 AM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9851322004</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.71579</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Sarveshwor Mahadev Temple, Nayabasti, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>03:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L31-6</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.36397</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:38 AM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333628</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9767216151</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 04:19:35 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>CHB9767216151</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 02:59:37 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:38:26 AM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>27.69999299027229, 85.34332452221567, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>9767216151@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L36-5</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>19h 18m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2926,12 +6264,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -2963,7 +6301,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -2973,7 +6311,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2984,7 +6322,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -2996,7 +6334,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13m</t>
+          <t>2h 2m</t>
         </is>
       </c>
     </row>
@@ -3008,7 +6346,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>14h 20m</t>
+          <t>12h 49m</t>
         </is>
       </c>
     </row>
@@ -3049,727 +6387,1737 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>87.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Replace SKYCOM to NETTV</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>nan%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Detailed Solved / Handled Tickets List</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1333983</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Sudharna Byanjankar</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 09:52:27 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:39:23 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>1h 35m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>12h 46m</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1333510</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Kabiraj Limbu</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>21h 31m</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333787</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Ganesh bahadur dhakal</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>15h 45m</t>
+          <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334079</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Bijaye Subedi</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:17:25 AM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>2h 48m</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1332693</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Girish Ojha</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>13 Sep 2026 04:22:39 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 5m</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1334100</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Abisesh Giri 1</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:05:49 AM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>2h 17m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>TKT1333983</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Sudharna Byanjankar</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:04:22 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:52:27 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:39:23 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>1h 35m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>12h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333510</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Kabiraj Limbu</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:24:32 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:55:56 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333787</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh bahadur dhakal</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 05:06:15 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:51:57 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>15h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334079</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Bijaye Subedi</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:17:25 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:06:08 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332693</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Girish Ojha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 04:22:39 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:28:00 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334100</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Abisesh Giri 1</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:05:49 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:22:50 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>2h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>TKT1334105</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Abhisesh Giri</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 09:09:34 AM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>2h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334172</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:58:03 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333455</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Ranjana jimee</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu
+(15 Sep 2026 01:31:35 PM) :
+Router has been upgraded
+TKT1333455
+9856022476
+Ranjana jimee
+New SN : ALCLFE4FE240
+Old SN : ALCLB2B212F3
+Note : Upgrade to wifi6
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 12:32:40 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:31:34 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>1d 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333363</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 11:24:30 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:47:59 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334089</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Arun Bhandari</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 08:40:37 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:27 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333526</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Uttam KC</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:36:58 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 01:34:08 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:21:58 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>23h 45m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>23h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333979</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>lavkush kumar mukhiya</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 09:49:30 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:13:52 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>14h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333912</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:56:46 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:27:57 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>17h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334125</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Niran Shahi Thakuri</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:28:19 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:46:14 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>3h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334129</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Uday Bhahadur Rana Magar</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:22:18 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:31:27 AM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:24:45 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1h 2m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334065</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Saradha Panta</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 07:57:11 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:08:55 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2954,10 +2954,8 @@
           <t>Dil Kumar Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9842097155</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9842097155</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2992,10 +2990,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.686495</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.686495</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3051,25 +3047,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>4,5</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.378118</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.378118</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3165,10 +3157,8 @@
           <t>Kushal Neupane</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9844064169</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9844064169</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3203,10 +3193,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.66527</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.66527</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3262,25 +3250,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB471</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3599</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.3599</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3376,10 +3360,8 @@
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9851150629</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9851150629</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3414,10 +3396,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.68817</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.68817</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3473,20 +3453,16 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB506</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.31543</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.31543000000001</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3589,8 @@
           <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851177792</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851177792</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3651,10 +3625,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.69393</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.69393</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3710,25 +3682,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L47-2</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.331616</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.331616</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3824,10 +3792,8 @@
           <t>Arun Bhandari</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9865297766</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9865297766</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3862,10 +3828,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.69864</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.69864</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3921,25 +3885,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L64-5</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.33317</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.33317</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4035,10 +3995,8 @@
           <t>Uttam KC</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9865667017</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9865667017</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4128,10 +4086,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4142,7 +4098,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4238,10 +4194,8 @@
           <t>lavkush kumar mukhiya</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9762420859</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9762420859</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4331,10 +4285,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4345,7 +4297,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4431,20 +4383,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Saroj Karki</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9869527479</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9869527479</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4516,10 +4462,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -4538,10 +4482,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4552,7 +4494,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4648,10 +4590,8 @@
           <t>Niran Shahi Thakuri</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9845603766</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9845603766</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4686,10 +4626,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.73941</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.73941</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4741,25 +4679,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB046</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.3076</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.30759999999999</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4855,10 +4789,8 @@
           <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9851070038</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9851070038</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4893,10 +4825,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.756502</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.756502</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4952,25 +4882,21 @@
           <t>Binod Dhami</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L10-3</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.317497</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.317497</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5066,10 +4992,8 @@
           <t>Madhukar Aryal</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9860752387</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9860752387</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5104,10 +5028,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.755555</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.755555</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5159,25 +5081,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>L41-8A</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.310901</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.310901</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5273,10 +5191,8 @@
           <t>Madhukar Aryal</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860752387</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860752387</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5311,10 +5227,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.755555</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.755555</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5366,25 +5280,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L41-8A</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.310901</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.310901</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5480,10 +5390,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5518,10 +5426,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5577,25 +5483,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5691,10 +5593,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5729,10 +5629,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5788,25 +5686,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5902,10 +5796,8 @@
           <t>Saradha Panta</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9851322004</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9851322004</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5940,10 +5832,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.71579</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.71579</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5999,25 +5889,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>L31-6</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.36397</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.36396999999999</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6113,10 +5999,8 @@
           <t>Biraj poudel</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9767216151</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9767216151</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6151,10 +6035,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6206,50 +6088,1300 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>L36-5</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>19h 18m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 38m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>19h 18m</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 38m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333868</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Lal Gurung</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Lal Gurung</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9848326369</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9848326369</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:06:45 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.7327</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near Middle Orbit Overseas Pvt. Ltd., P8M9+588, Kathmandu 44611, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>ganesh@laundryunion.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>04:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.3181</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>18h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333879</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Rekha rawat</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Rekha rawat</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9863329493</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:01 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9863329493</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:20:59 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:01 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.686798646165148, 85.2887221697945, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>19h 5m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW28" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Slow internet</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333628</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9767216151</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>CHB9767216151</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 02:59:37 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>27.69999299027229, 85.34332452221567, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>9767216151@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>09:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L36-5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334223</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Magar</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Magar</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9808791830</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9808791830</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:26:08 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:50:45 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.73618</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Tudaldevi Marg,Tudaldevi Temple, Kathmandu,, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>bjp.thito@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L21-2</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.32829</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>11m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>3h 24m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:17 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333699</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9851022984</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9851022984</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:17:52 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70788</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Near Ratna Store, Chhauni, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>nepaltravellink@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>08:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB384</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.29744</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334316</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9813456223</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9880059826</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:57:47 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.71182</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Near Little Buddha's Academy,Bijeshowri, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>rawmaashrestha456@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>02:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB248</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.29671</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6264,7 +7396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6301,7 +7433,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6311,7 +7443,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -6322,7 +7454,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.8%</t>
         </is>
       </c>
     </row>
@@ -6334,7 +7466,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 2m</t>
+          <t>2h 38m</t>
         </is>
       </c>
     </row>
@@ -6346,7 +7478,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>12h 49m</t>
+          <t>13h 5m</t>
         </is>
       </c>
     </row>
@@ -6387,14 +7519,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -6459,14 +7591,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6531,14 +7663,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -6669,14 +7801,14 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7272,7 +8404,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -7339,7 +8471,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -7484,7 +8616,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -7551,7 +8683,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -7618,7 +8750,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -7685,7 +8817,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -7752,7 +8884,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7819,7 +8951,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -7886,7 +9018,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -7953,7 +9085,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -8020,7 +9152,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -8087,14 +9219,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:08:55 PM</t>
@@ -8118,6 +9250,341 @@
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>5h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333868</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Ganesh Lal Gurung</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:06:45 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:01:58 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>18h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333628</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Biraj poudel</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 02:59:37 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:26:43 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>23h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334223</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Magar</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:39:14 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:26:08 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:50:45 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>11m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>3h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333699</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:17:52 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334316</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:57:47 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6198,10 +6198,8 @@
           <t>Ganesh Lal Gurung</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9848326369</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9848326369</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6236,10 +6234,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.7327</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.7327</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6295,25 +6291,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.3181</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.3181</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6409,10 +6401,8 @@
           <t>Rekha rawat</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9863329493</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9863329493</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6480,10 +6470,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH30" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH30" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="inlineStr"/>
@@ -6498,10 +6486,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6512,7 +6498,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6608,10 +6594,8 @@
           <t>Biraj poudel</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9767216151</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9767216151</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6646,10 +6630,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6705,25 +6687,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L36-5</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6819,10 +6797,8 @@
           <t>Srijana Magar</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9808791830</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9808791830</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6857,10 +6833,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.73618</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.73618</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6916,25 +6890,21 @@
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L21-2</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.32829</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.32829</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7030,10 +7000,8 @@
           <t>Lok Parsad Silwal</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9851022984</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9851022984</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7068,10 +7036,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70788</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70788</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7127,25 +7093,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB384</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.29744</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.29743999999999</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7241,10 +7203,8 @@
           <t>Rama Shrestha</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9813456223</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9813456223</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7279,10 +7239,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.71182</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.71182</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7338,48 +7296,657 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB248</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.29671</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.29671</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>2h 42m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>2h 42m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:46 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333643</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9851182604</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9851182604</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:46:25 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Sanskar Shikshyalaya - Preschool Tahachal Marg Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>memanishktm125@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>09:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334567</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>kshitij kafle</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>kshitij kafle</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9814791201</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:43:02 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>BKT9814791201</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:39:20 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:52:13 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>27.65607,85.37356, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>kshitijkafle21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 2:47 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334492</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Kumar Karki</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Kumar Karki</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9845130442</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9851079644</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:43:35 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.67179</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Narephate ward no:32, Kotdevi marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>sudhapolyclinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB555</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.34593</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7396,7 +7963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7433,7 +8000,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -7443,7 +8010,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -7454,7 +8021,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -7466,7 +8033,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 38m</t>
+          <t>3h 19m</t>
         </is>
       </c>
     </row>
@@ -7478,7 +8045,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>13h 5m</t>
+          <t>13h 4m</t>
         </is>
       </c>
     </row>
@@ -7519,14 +8086,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -7537,14 +8104,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7663,14 +8230,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -7723,12 +8290,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -7751,233 +8318,189 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333983</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Sudharna Byanjankar</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 09:52:27 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:39:23 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>1h 35m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>12h 46m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1333510</t>
+          <t>TKT1333983</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Kabiraj Limbu</t>
+          <t>Sudharna Byanjankar</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7992,12 +8515,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -8007,44 +8530,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
+          <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8079,17 +8602,17 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -8099,19 +8622,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>15h 45m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1334079</t>
+          <t>TKT1333787</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Bijaye Subedi</t>
+          <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -8141,22 +8664,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:17:25 AM</t>
+          <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -8166,19 +8689,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>15h 45m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1332693</t>
+          <t>TKT1334079</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Girish Ojha</t>
+          <t>Bijaye Subedi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -8208,22 +8731,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>13 Sep 2026 04:22:39 PM</t>
+          <t>15 Sep 2026 08:17:25 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -8233,19 +8756,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 5m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1334100</t>
+          <t>TKT1332693</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Abisesh Giri 1</t>
+          <t>Girish Ojha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8275,22 +8798,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:05:49 AM</t>
+          <t>13 Sep 2026 04:22:39 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8300,19 +8823,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2h 17m</t>
+          <t>1d 19h 5m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334105</t>
+          <t>TKT1334100</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Abhisesh Giri</t>
+          <t>Abisesh Giri 1</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8347,17 +8870,17 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:09:34 AM</t>
+          <t>15 Sep 2026 09:05:49 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -8367,29 +8890,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2h 8m</t>
+          <t>2h 17m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1334172</t>
+          <t>TKT1334105</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dil Kumar Shrestha</t>
+          <t>Abhisesh Giri</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -8409,22 +8932,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:58:03 AM</t>
+          <t>15 Sep 2026 09:09:34 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -8434,29 +8957,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1333648</t>
+          <t>TKT1334172</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Dil Kumar Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8476,22 +8999,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:17:35 PM</t>
+          <t>15 Sep 2026 09:58:03 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -8501,42 +9024,109 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 29m</t>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>TKT1333455</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu
 (15 Sep 2026 01:31:35 PM) :
@@ -8552,113 +9142,46 @@
 Related Documents</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 12:32:40 PM</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>1d 58m</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333363</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Kanunalaya Inc. Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 11:24:30 AM</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1334089</t>
+          <t>TKT1333363</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Arun Bhandari</t>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -8668,7 +9191,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -8688,22 +9211,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:40:37 AM</t>
+          <t>14 Sep 2026 11:24:30 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -8713,19 +9236,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1333526</t>
+          <t>TKT1334089</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Uttam KC</t>
+          <t>Arun Bhandari</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -8735,17 +9258,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -8755,44 +9278,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:36:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:34:08 PM</t>
+          <t>15 Sep 2026 08:40:37 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:21:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>23h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>23h 47m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1333979</t>
+          <t>TKT1333526</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>lavkush kumar mukhiya</t>
+          <t>Uttam KC</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -8822,44 +9345,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:36:58 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:34:08 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:13:52 PM</t>
+          <t>15 Sep 2026 01:21:58 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 45m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 47m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1333912</t>
+          <t>TKT1333979</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Saroj Karki</t>
+          <t>lavkush kumar mukhiya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8874,12 +9397,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8889,44 +9412,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:56:46 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>15 Sep 2026 12:13:52 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>14h 24m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>17h 31m</t>
+          <t>14h 24m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334125</t>
+          <t>TKT1333912</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Niran Shahi Thakuri</t>
+          <t>Saroj Karki</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8956,22 +9479,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:28:19 AM</t>
+          <t>14 Sep 2026 07:56:46 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -8981,19 +9504,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>3h 17m</t>
+          <t>17h 31m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1334129</t>
+          <t>TKT1334125</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Uday Bhahadur Rana Magar</t>
+          <t>Niran Shahi Thakuri</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -9008,12 +9531,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -9023,44 +9546,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:22:18 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:31:27 AM</t>
+          <t>15 Sep 2026 09:28:19 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:24:45 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1h 2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 17m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1334129</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -9075,12 +9598,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -9090,32 +9613,32 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:22:18 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 09:31:27 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 01:24:45 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 2m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>5h 11m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
@@ -9256,12 +9779,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1333868</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Lal Gurung</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -9286,27 +9809,27 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:06:45 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -9316,29 +9839,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>18h 55m</t>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1333628</t>
+          <t>TKT1333868</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Biraj poudel</t>
+          <t>Ganesh Lal Gurung</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -9353,27 +9876,27 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 02:59:37 PM</t>
+          <t>14 Sep 2026 07:06:45 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -9383,86 +9906,86 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>23h 27m</t>
+          <t>18h 55m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1334223</t>
+          <t>TKT1333628</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Srijana Magar</t>
+          <t>Biraj poudel</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:39:14 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:26:08 AM</t>
+          <t>14 Sep 2026 02:59:37 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:50:45 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>3h 24m</t>
+          <t>23h 27m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1333699</t>
+          <t>TKT1334223</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Lok Parsad Silwal</t>
+          <t>Srijana Magar</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -9487,104 +10010,305 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 01:39:14 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 10:26:08 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:17:52 PM</t>
+          <t>15 Sep 2026 01:50:45 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>3h 24m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>TKT1333699</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Lok Parsad Silwal</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:49:03 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:17:52 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>TKT1334316</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Rama Shrestha</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:57:47 PM</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>2h 42m</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>2h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333643</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:46:25 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334492</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Dipak Kumar Karki</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:43:35 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW37"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -513,17 +513,17 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="32" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -7406,10 +7406,8 @@
           <t>Manish Agrawal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9851182604</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9851182604</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7499,10 +7497,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7513,7 +7509,7 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7609,10 +7605,8 @@
           <t>kshitij kafle</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9814791201</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9814791201</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7698,10 +7692,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -7712,7 +7704,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7808,10 +7800,8 @@
           <t>Dipak Kumar Karki</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9845130442</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9845130442</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7846,10 +7836,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.67179</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.67179</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -7905,48 +7893,2142 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB555</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.34593</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.34593</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:01 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Iptv issue</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334031</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Gautam shrestha</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Gautam shrestha</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9851059167</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9851059167</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:10:23 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.742284</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Bandari tole numble boarding, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>05:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L61-3</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.316966</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 3m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>8h 51m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334441</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sunshine Tradelink</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sunshine Tradelink</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9851015418</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9851015418</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:14:10 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.718612</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Lainchaur Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.315203</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>3h 44m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334146</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Ajib Shrestha</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Ajib Shrestha</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9808961772</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9808961772</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:43:57 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.70676</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Shovabhagwati -15, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>ajib.she.50@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>05:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.29837</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>6h 13m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:15 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334668</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Tamrakar</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9851075215</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:40:42 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9843637315</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:27:57 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:40:42 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.7126</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Swoyambhu Dallu  ward no:15 near Shree Jal Ganesh Pasa Pucha Saving &amp; Credit Co-operative Ltd., Bagm</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>asinam3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.30076</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1h 12m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334656</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Ashok Budal</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Ashok Budal</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9848400804</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9848400804</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:18:04 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.687</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Near Treasure Music Store,Santinagar,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>ashok.budal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>01:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L17-5</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.34223</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1h 39m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334472</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Dhungel</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Dhungel</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9865072901</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9865072901</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.6962</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>P98F+FPW, Gokarneshwor 44600,kATHMANDU, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>dhungelpramod05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L64-6</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.34991</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:48 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.70966</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila near Miracle International Model Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>magarsuman375@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>04:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.27402</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9861757307</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.70966</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila near Miracle International Model Academy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>magarsuman375@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>04:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.27402</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:07 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Wif 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334295</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9860189978</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9802238348</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:07:09 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.69723</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School Purano Kalimati, Bafal, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>khadkanisha4444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB332</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.283</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 5m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334280</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:00:23 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.699615</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School - School Purano Kalimati Bafal Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>9866115651m@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>04:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.284092</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7963,13 +10045,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -8000,7 +10082,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -8010,7 +10092,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -8021,7 +10103,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -8033,7 +10115,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 19m</t>
+          <t>2h 57m</t>
         </is>
       </c>
     </row>
@@ -8045,7 +10127,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>13h 4m</t>
+          <t>11h 9m</t>
         </is>
       </c>
     </row>
@@ -8086,14 +10168,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -8104,14 +10186,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8122,14 +10204,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8230,14 +10312,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -8295,30 +10377,30 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -8341,300 +10423,212 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1333983</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Sudharna Byanjankar</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 09:52:27 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:39:23 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>1h 35m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333510</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Kabiraj Limbu</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>21h 31m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1333983</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Sudharna Byanjankar</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -8649,12 +10643,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -8664,44 +10658,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>15h 45m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1334079</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Bijaye Subedi</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -8731,22 +10725,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:17:25 AM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -8756,19 +10750,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1332693</t>
+          <t>TKT1333787</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Girish Ojha</t>
+          <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8798,22 +10792,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>13 Sep 2026 04:22:39 PM</t>
+          <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8823,19 +10817,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 5m</t>
+          <t>15h 45m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334100</t>
+          <t>TKT1334079</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Abisesh Giri 1</t>
+          <t>Bijaye Subedi</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8865,22 +10859,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:05:49 AM</t>
+          <t>15 Sep 2026 08:17:25 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -8890,19 +10884,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2h 17m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1334105</t>
+          <t>TKT1332693</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Abhisesh Giri</t>
+          <t>Girish Ojha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -8932,22 +10926,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:09:34 AM</t>
+          <t>13 Sep 2026 04:22:39 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -8957,29 +10951,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 8m</t>
+          <t>1d 19h 5m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1334172</t>
+          <t>TKT1334100</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Dil Kumar Shrestha</t>
+          <t>Abisesh Giri 1</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8999,22 +10993,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:58:03 AM</t>
+          <t>15 Sep 2026 09:05:49 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9024,29 +11018,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>2h 17m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1333648</t>
+          <t>TKT1334105</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Abhisesh Giri</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9066,22 +11060,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:17:35 PM</t>
+          <t>15 Sep 2026 09:09:34 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9091,42 +11085,176 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 29m</t>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TKT1334172</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Dil Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:58:03 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:34:16 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>TKT1333455</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu
 (15 Sep 2026 01:31:35 PM) :
@@ -9142,180 +11270,46 @@
 Related Documents</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 12:32:40 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>1d 58m</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>TKT1333363</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Kanunalaya Inc. Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 11:24:30 AM</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>1d 1h 23m</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>TKT1334089</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Arun Bhandari</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade Dual Band</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 08:40:37 AM</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1333526</t>
+          <t>TKT1333363</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Uttam KC</t>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -9330,12 +11324,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9345,44 +11339,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:36:58 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:34:08 PM</t>
+          <t>14 Sep 2026 11:24:30 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:21:58 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>23h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>23h 47m</t>
+          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1333979</t>
+          <t>TKT1334089</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>lavkush kumar mukhiya</t>
+          <t>Arun Bhandari</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9392,17 +11386,17 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -9412,44 +11406,44 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>15 Sep 2026 08:40:37 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:13:52 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1333912</t>
+          <t>TKT1333526</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Saroj Karki</t>
+          <t>Uttam KC</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -9464,12 +11458,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9479,44 +11473,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>14 Sep 2026 01:36:58 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:56:46 PM</t>
+          <t>14 Sep 2026 01:34:08 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>15 Sep 2026 01:21:58 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 45m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>17h 31m</t>
+          <t>23h 47m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1334125</t>
+          <t>TKT1333979</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Niran Shahi Thakuri</t>
+          <t>lavkush kumar mukhiya</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -9531,12 +11525,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -9546,44 +11540,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:28:19 AM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 12:13:52 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>14h 24m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>3h 17m</t>
+          <t>14h 24m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1334129</t>
+          <t>TKT1333912</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Uday Bhahadur Rana Magar</t>
+          <t>Saroj Karki</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -9598,12 +11592,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -9613,44 +11607,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:22:18 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:31:27 AM</t>
+          <t>14 Sep 2026 07:56:46 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:24:45 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>1h 2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>17h 31m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1334125</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Niran Shahi Thakuri</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9680,22 +11674,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 09:28:19 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9705,19 +11699,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>5h 11m</t>
+          <t>3h 17m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1334129</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -9732,12 +11726,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -9747,32 +11741,32 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:22:18 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 09:31:27 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 01:24:45 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 2m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>5h 11m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
@@ -9846,12 +11840,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1333868</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Lal Gurung</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -9881,22 +11875,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:06:45 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -9906,29 +11900,29 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>18h 55m</t>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1333628</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Biraj poudel</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -9948,22 +11942,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 02:59:37 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -9973,19 +11967,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>23h 27m</t>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1334223</t>
+          <t>TKT1333868</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Srijana Magar</t>
+          <t>Ganesh Lal Gurung</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10000,12 +11994,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -10015,64 +12009,64 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:39:14 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:26:08 AM</t>
+          <t>14 Sep 2026 07:06:45 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:50:45 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>3h 24m</t>
+          <t>18h 55m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1333699</t>
+          <t>TKT1333628</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Lok Parsad Silwal</t>
+          <t>Biraj poudel</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -10082,44 +12076,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>14 Sep 2026 02:59:37 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:17:52 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>23h 27m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1334316</t>
+          <t>TKT1334223</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Rama Shrestha</t>
+          <t>Srijana Magar</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -10149,44 +12143,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>15 Sep 2026 01:39:14 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>15 Sep 2026 10:26:08 AM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:57:47 PM</t>
+          <t>15 Sep 2026 01:50:45 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>3h 24m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1333643</t>
+          <t>TKT1333699</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Manish Agrawal</t>
+          <t>Lok Parsad Silwal</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -10211,104 +12205,774 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:46:25 PM</t>
+          <t>15 Sep 2026 02:17:52 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>22h 28m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
+          <t>TKT1334316</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Rama Shrestha</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:15:01 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:57:47 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333643</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Manish Agrawal</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:15:17 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:46:25 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>23h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>TKT1334492</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Dipak Kumar Karki</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:43:35 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:47:15 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>2h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334031</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Gautam shrestha</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:10:23 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>8h 51m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334441</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Sunshine Tradelink</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:14:10 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:40 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>3h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334146</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Ajib Shrestha</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:43:57 AM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:42 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>6h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334656</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Ashok Budal</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:43:35 PM</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:18:04 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:57:31 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>2h 3m</t>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334472</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Dhungel</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:23:50 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334285</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Suman Darlami Magar</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:53:46 AM</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:48:09 PM</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334280</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:00:23 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7993,20 +7993,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Gautam shrestha</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9851059167</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9851059167</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8041,10 +8035,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.742284</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.742284</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8096,25 +8088,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>L61-3</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.316966</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.31696599999999</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8210,10 +8198,8 @@
           <t>Sunshine Tradelink</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9851015418</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9851015418</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8248,10 +8234,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>27.718612</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>27.718612</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -8303,25 +8287,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.315203</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.315203</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8417,10 +8397,8 @@
           <t>Ajib Shrestha</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9808961772</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9808961772</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8455,10 +8433,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.70676</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.70676</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -8496,10 +8472,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH40" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH40" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
@@ -8518,25 +8492,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.29837</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.29837000000001</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8632,10 +8602,8 @@
           <t>Manisha Tamrakar</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9851075215</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9851075215</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8670,10 +8638,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.7126</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.7126</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8725,25 +8691,21 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.30076</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30076</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8839,10 +8801,8 @@
           <t>Ashok Budal</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9848400804</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9848400804</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8877,10 +8837,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.687</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.687</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8936,25 +8894,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L17-5</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.34223</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.34223</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9050,10 +9004,8 @@
           <t>Pramod Dhungel</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9865072901</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9865072901</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9088,10 +9040,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.6962</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.6962</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9147,25 +9097,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L64-6</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.34991</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.34990999999999</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9251,20 +9197,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Suman Darlami Magar</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9861757307</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9861757307</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9299,10 +9239,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.70966</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.70966</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9358,25 +9296,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.27402</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.27401999999999</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9462,20 +9396,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
           <t>Suman Darlami Magar</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9861757307</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9861757307</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9510,10 +9438,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.70966</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.70966</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9569,25 +9495,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.27402</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.27401999999999</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9683,10 +9605,8 @@
           <t>Amin Karki</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9860189978</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9860189978</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9721,10 +9641,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.69723</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.69723</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -9776,25 +9694,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB332</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.283</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.283</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9890,10 +9804,8 @@
           <t>Gopal Prasad Dhakal</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9866115651</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9866115651</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9928,10 +9840,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.699615</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.699615</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9987,50 +9897,257 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.284092</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.284092</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>4h 9m</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>4h 9m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Wif 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334295</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9860189978</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9802238348</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:19:22 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.69723</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Gyanodaya Secondary School Purano Kalimati, Bafal, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>khadkanisha4444@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>05:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB332</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.283</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -10045,7 +10162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10082,7 +10199,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -10092,7 +10209,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10103,7 +10220,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10232,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 57m</t>
+          <t>3h 1m</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10244,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11h 9m</t>
+          <t>10h 59m</t>
         </is>
       </c>
     </row>
@@ -10168,14 +10285,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -10312,14 +10429,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12590,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -12540,7 +12657,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -12607,7 +12724,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -12674,7 +12791,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -12741,7 +12858,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -12808,7 +12925,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -12875,7 +12992,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -12942,14 +13059,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:50:35 AM</t>
@@ -12973,6 +13090,73 @@
       <c r="M67" s="5" t="inlineStr">
         <is>
           <t>4h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334295</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Amin Karki</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:01:44 AM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:19:22 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10007,10 +10007,8 @@
           <t>Amin Karki</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9860189978</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9860189978</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10045,10 +10043,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.69723</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.69723</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -10104,50 +10100,1077 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB332</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.283</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.283</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>5h 17m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>5h 17m</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>5h 17m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:58 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334762</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Junkeri ale Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Junkeri ale Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9841034591</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9841034591</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:36:15 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Tenzing Chowk - Bus stop Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>junkerialeshrestha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>01:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1h 22m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334412</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Kishwor Khanal</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:22:53 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9843123637</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 12:00:05 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:09:04 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.705894</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Purnima Press Details from Google Maps P844+M85, Sahid Nigurna Marg, Kathmandu 44600, Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>CDB288</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.306163</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>46m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>5h 8m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334529</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Sen Thakuri</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Bhim Sen Thakuri</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9861847418</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9861847418</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:21 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.716731</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Near Bishwa Shiksha Sadan Secondary School (Montessori Based School), Shankar, Boudhanath Marg, Kath</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>thakuribhimsen@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>03:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L5-6</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.349705</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:02 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334791</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>INDIRA RANABHAT</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>INDIRA RANABHAT</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9866471440</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9860365129</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:52:57 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.665254</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>27.665254, 85.374492, Ranabhat toll, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>01:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L1-1</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.374492</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 4:41 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334532</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Om parkash</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Om parkash</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9851227421</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:41:39 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9851227421</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:54 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:07:27 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.657558</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinayak-3, Balkot Details from Google Maps M98J+72Q, Anantalingeshwar View in Google Maps, Bhak</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr"/>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>03:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Govinda Chaulagain</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L36-1</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.319703</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -10162,7 +11185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10199,7 +11222,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -10209,7 +11232,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -10220,7 +11243,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -10232,7 +11255,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 1m</t>
+          <t>2h 44m</t>
         </is>
       </c>
     </row>
@@ -10244,7 +11267,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10h 59m</t>
+          <t>10h 9m</t>
         </is>
       </c>
     </row>
@@ -10285,14 +11308,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -10303,14 +11326,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10321,14 +11344,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -10429,14 +11452,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -10498,10 +11521,10 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -10540,7 +11563,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -10563,18 +11586,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -10586,7 +11609,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -10604,215 +11627,171 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1333983</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Sudharna Byanjankar</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 09:52:27 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:39:23 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>1h 35m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>12h 46m</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1333510</t>
+          <t>TKT1333983</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Kabiraj Limbu</t>
+          <t>Sudharna Byanjankar</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -10827,12 +11806,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -10842,44 +11821,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
+          <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -10914,17 +11893,17 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -10934,19 +11913,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>15h 45m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1334079</t>
+          <t>TKT1333787</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bijaye Subedi</t>
+          <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -10976,22 +11955,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:17:25 AM</t>
+          <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -11001,19 +11980,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>15h 45m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1332693</t>
+          <t>TKT1334079</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Girish Ojha</t>
+          <t>Bijaye Subedi</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -11043,22 +12022,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>13 Sep 2026 04:22:39 PM</t>
+          <t>15 Sep 2026 08:17:25 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -11068,19 +12047,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 5m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1334100</t>
+          <t>TKT1332693</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Abisesh Giri 1</t>
+          <t>Girish Ojha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -11110,22 +12089,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:05:49 AM</t>
+          <t>13 Sep 2026 04:22:39 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -11135,19 +12114,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2h 17m</t>
+          <t>1d 19h 5m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1334105</t>
+          <t>TKT1334100</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Abhisesh Giri</t>
+          <t>Abisesh Giri 1</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -11182,17 +12161,17 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:09:34 AM</t>
+          <t>15 Sep 2026 09:05:49 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -11202,29 +12181,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2h 8m</t>
+          <t>2h 17m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1334172</t>
+          <t>TKT1334105</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Dil Kumar Shrestha</t>
+          <t>Abhisesh Giri</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -11244,22 +12223,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:58:03 AM</t>
+          <t>15 Sep 2026 09:09:34 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -11269,29 +12248,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1333648</t>
+          <t>TKT1334172</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Dil Kumar Shrestha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -11311,22 +12290,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:17:35 PM</t>
+          <t>15 Sep 2026 09:58:03 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -11336,42 +12315,109 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 29m</t>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>TKT1333455</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Chandramani Tharu
 (15 Sep 2026 01:31:35 PM) :
@@ -11387,113 +12433,46 @@
 Related Documents</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>14 Sep 2026 12:32:40 PM</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>1d 58m</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>TKT1333363</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Kanunalaya Inc. Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 11:24:30 AM</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1334089</t>
+          <t>TKT1333363</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Arun Bhandari</t>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -11503,7 +12482,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -11523,22 +12502,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:40:37 AM</t>
+          <t>14 Sep 2026 11:24:30 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -11548,19 +12527,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1333526</t>
+          <t>TKT1334089</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Uttam KC</t>
+          <t>Arun Bhandari</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11570,17 +12549,17 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -11590,44 +12569,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:36:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:34:08 PM</t>
+          <t>15 Sep 2026 08:40:37 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:21:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>23h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>23h 47m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1333979</t>
+          <t>TKT1333526</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>lavkush kumar mukhiya</t>
+          <t>Uttam KC</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11657,44 +12636,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:36:58 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:34:08 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:13:52 PM</t>
+          <t>15 Sep 2026 01:21:58 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 45m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 47m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1333912</t>
+          <t>TKT1333979</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Saroj Karki</t>
+          <t>lavkush kumar mukhiya</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11709,12 +12688,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -11724,44 +12703,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:56:46 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>15 Sep 2026 12:13:52 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>14h 24m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>17h 31m</t>
+          <t>14h 24m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1334125</t>
+          <t>TKT1333912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Niran Shahi Thakuri</t>
+          <t>Saroj Karki</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -11791,22 +12770,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:28:19 AM</t>
+          <t>14 Sep 2026 07:56:46 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -11816,19 +12795,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>3h 17m</t>
+          <t>17h 31m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1334129</t>
+          <t>TKT1334125</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Uday Bhahadur Rana Magar</t>
+          <t>Niran Shahi Thakuri</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -11843,12 +12822,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -11858,44 +12837,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:22:18 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:31:27 AM</t>
+          <t>15 Sep 2026 09:28:19 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:24:45 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>1h 2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 17m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1334129</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11910,12 +12889,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -11925,32 +12904,32 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:22:18 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 09:31:27 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 01:24:45 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 2m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>5h 11m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
@@ -12091,12 +13070,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1333868</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Ganesh Lal Gurung</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -12126,22 +13105,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:06:45 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -12151,29 +13130,29 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>18h 55m</t>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1333628</t>
+          <t>TKT1333868</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Biraj poudel</t>
+          <t>Ganesh Lal Gurung</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -12193,22 +13172,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 02:59:37 PM</t>
+          <t>14 Sep 2026 07:06:45 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -12218,39 +13197,39 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>23h 27m</t>
+          <t>18h 55m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1334223</t>
+          <t>TKT1333628</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Srijana Magar</t>
+          <t>Biraj poudel</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -12260,44 +13239,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:39:14 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:26:08 AM</t>
+          <t>14 Sep 2026 02:59:37 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:50:45 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>3h 24m</t>
+          <t>23h 27m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1333699</t>
+          <t>TKT1334223</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Lok Parsad Silwal</t>
+          <t>Srijana Magar</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12327,44 +13306,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 01:39:14 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 10:26:08 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:17:52 PM</t>
+          <t>15 Sep 2026 01:50:45 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>3h 24m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1334316</t>
+          <t>TKT1333699</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Rama Shrestha</t>
+          <t>Lok Parsad Silwal</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -12394,44 +13373,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:57:47 PM</t>
+          <t>15 Sep 2026 02:17:52 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>22h 28m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1333643</t>
+          <t>TKT1334316</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Manish Agrawal</t>
+          <t>Rama Shrestha</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12461,44 +13440,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:46:25 PM</t>
+          <t>15 Sep 2026 01:57:47 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>2h 42m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>2h 42m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1334492</t>
+          <t>TKT1333643</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Dipak Kumar Karki</t>
+          <t>Manish Agrawal</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12513,12 +13492,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -12528,54 +13507,54 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
+          <t>14 Sep 2026 03:15:17 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:43:35 PM</t>
+          <t>14 Sep 2026 03:15:17 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
+          <t>15 Sep 2026 02:46:25 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 31m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>2h 3m</t>
+          <t>23h 31m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1334031</t>
+          <t>TKT1334492</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Gautam shrestha</t>
+          <t>Dipak Kumar Karki</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -12595,22 +13574,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:01:53 PM</t>
+          <t>15 Sep 2026 02:47:15 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:10:23 AM</t>
+          <t>15 Sep 2026 12:43:35 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:01:53 PM</t>
+          <t>15 Sep 2026 02:47:15 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -12620,29 +13599,29 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>8h 51m</t>
+          <t>2h 3m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1334441</t>
+          <t>TKT1334031</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Sunshine Tradelink</t>
+          <t>Gautam shrestha</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -12662,22 +13641,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:58:40 PM</t>
+          <t>15 Sep 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:14:10 PM</t>
+          <t>15 Sep 2026 06:10:23 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:58:40 PM</t>
+          <t>15 Sep 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -12687,19 +13666,19 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>3h 44m</t>
+          <t>8h 51m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1334146</t>
+          <t>TKT1334441</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Ajib Shrestha</t>
+          <t>Sunshine Tradelink</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -12729,22 +13708,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:42 PM</t>
+          <t>15 Sep 2026 03:58:40 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:43:57 AM</t>
+          <t>15 Sep 2026 12:14:10 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:42 PM</t>
+          <t>15 Sep 2026 03:58:40 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -12754,19 +13733,19 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>6h 13m</t>
+          <t>3h 44m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1334656</t>
+          <t>TKT1334146</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Ashok Budal</t>
+          <t>Ajib Shrestha</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -12796,22 +13775,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:31 PM</t>
+          <t>15 Sep 2026 03:57:42 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:18:04 PM</t>
+          <t>15 Sep 2026 09:43:57 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:31 PM</t>
+          <t>15 Sep 2026 03:57:42 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -12821,29 +13800,29 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>6h 13m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1334472</t>
+          <t>TKT1334656</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Pramod Dhungel</t>
+          <t>Ashok Budal</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -12863,22 +13842,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:23:50 PM</t>
+          <t>15 Sep 2026 03:57:31 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:28:17 PM</t>
+          <t>15 Sep 2026 02:18:04 PM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:23:50 PM</t>
+          <t>15 Sep 2026 03:57:31 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -12888,39 +13867,39 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2h 55m</t>
+          <t>1h 39m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1334285</t>
+          <t>TKT1334472</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Suman Darlami Magar</t>
+          <t>Pramod Dhungel</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -12930,32 +13909,32 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:53:46 AM</t>
+          <t>15 Sep 2026 03:23:50 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:53:46 AM</t>
+          <t>15 Sep 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:48:09 PM</t>
+          <t>15 Sep 2026 03:23:50 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>4h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>4h 54m</t>
+          <t>2h 55m</t>
         </is>
       </c>
     </row>
@@ -13029,12 +14008,12 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1334280</t>
+          <t>TKT1334285</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Gopal Prasad Dhakal</t>
+          <t>Suman Darlami Magar</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -13064,99 +14043,434 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:50:35 AM</t>
+          <t>15 Sep 2026 10:53:46 AM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:50:35 AM</t>
+          <t>15 Sep 2026 10:53:46 AM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:00:23 PM</t>
+          <t>15 Sep 2026 03:48:09 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>4h 9m</t>
+          <t>4h 54m</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>4h 9m</t>
+          <t>4h 54m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>TKT1334280</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Gopal Prasad Dhakal</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:50:35 AM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:00:23 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>4h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>TKT1334295</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Amin Karki</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:01:44 AM</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 11:01:44 AM</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 04:19:22 PM</t>
         </is>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>5h 17m</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>5h 17m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334762</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Junkeri ale Shrestha</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:36:15 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:58:24 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>1h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334529</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Bhim Sen Thakuri</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:21 PM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:10:54 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>3h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334791</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>INDIRA RANABHAT</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:52:57 PM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>1h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334532</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Om parkash</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:41:39 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 01:12:54 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:07:27 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -10210,10 +10210,8 @@
           <t>Junkeri ale Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9841034591</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9841034591</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10303,10 +10301,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -10317,7 +10313,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10413,10 +10409,8 @@
           <t>Kishwor Khanal</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9843123637</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9843123637</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10451,10 +10445,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.705894</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.705894</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10502,25 +10494,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>CDB288</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.306163</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.306163</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -10616,10 +10604,8 @@
           <t>Bhim Sen Thakuri</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9861847418</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9861847418</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10654,10 +10640,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.716731</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.716731</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -10713,25 +10697,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L5-6</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.349705</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.349705</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10827,10 +10807,8 @@
           <t>INDIRA RANABHAT</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9866471440</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9866471440</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10865,10 +10843,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.665254</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.665254</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10920,25 +10896,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L1-1</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.374492</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.374492</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -11034,10 +11006,8 @@
           <t>Om parkash</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9851227421</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9851227421</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11072,10 +11042,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.657558</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.657558</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -11127,25 +11095,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>L36-1</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.319703</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.319703</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -14239,7 +14203,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -14306,7 +14270,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -14373,7 +14337,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -14440,7 +14404,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11138,6 +11138,639 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:45 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:44 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 5:21 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9851041494</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.74613</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Ram Mandir Heights Details from Google Maps Unnamed Road, P9R5+X58, ??????????? 44600 , Bagmati, Cen</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>rajkc6431@gmal.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>00:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>L27-8</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.36217</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11149,7 +11782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11186,7 +11819,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -11196,7 +11829,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -11207,7 +11840,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11852,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 44m</t>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11864,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10h 9m</t>
+          <t>9h 30m</t>
         </is>
       </c>
     </row>
@@ -11272,14 +11905,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -11416,14 +12049,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -14438,6 +15071,207 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW56"/>
+  <dimension ref="A1:AW57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11205,10 +11205,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11243,10 +11241,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -11302,25 +11298,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11416,10 +11408,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11454,10 +11444,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11513,25 +11501,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11627,10 +11611,8 @@
           <t>Raj KC</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9851041494</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9851041494</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11665,10 +11647,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>27.74613</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>27.74613</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -11724,50 +11704,253 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>L27-8</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.36217</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.36217000000001</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:15 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334286</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Yognath dhakal</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Yognath dhakal</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9749324717</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9749324717</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:56:26 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.7229</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Thali gajarkot, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr"/>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>07:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>L53-6</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.410785</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>58m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>7h 18m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11819,7 +12002,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -11829,7 +12012,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -11840,7 +12023,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -11852,7 +12035,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 32m</t>
+          <t>2h 29m</t>
         </is>
       </c>
     </row>
@@ -11864,7 +12047,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9h 30m</t>
+          <t>9h 27m</t>
         </is>
       </c>
     </row>
@@ -11905,14 +12088,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -12049,14 +12232,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15287,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -15171,7 +15354,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -15238,14 +15421,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
           <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 05:44:50 PM</t>
@@ -15269,6 +15452,73 @@
       <c r="M76" s="3" t="inlineStr">
         <is>
           <t>58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334286</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Yognath dhakal</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:56:26 AM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:15:02 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>7h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -11814,10 +11814,8 @@
           <t>Yognath dhakal</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9749324717</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9749324717</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11852,10 +11850,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.7229</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.7229</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11907,25 +11903,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>L53-6</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.410785</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.410785</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -15488,7 +15480,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW57"/>
+  <dimension ref="A1:AW60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11946,6 +11946,627 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:47 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>sky com to net tv</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1333865</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9818723103</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Near Stupa Butcher Shop, M895+5M5, ?????????? ???, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr"/>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>09:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:43 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>ssid auto disconnect</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9709029533</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709029533</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>27.6744679, 85.2724591, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>9709029533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>08:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB226</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:42 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>ssid auto disconnect</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9709029533</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709029533</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>27.6744679, 85.2724591, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>9709029533@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>08:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>CDB226</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11957,7 +12578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11994,7 +12615,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -12004,7 +12625,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -12015,7 +12636,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12648,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 29m</t>
+          <t>2h 26m</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12660,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9h 27m</t>
+          <t>9h 42m</t>
         </is>
       </c>
     </row>
@@ -12116,14 +12737,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -12134,14 +12755,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -12362,14 +12983,14 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -12427,210 +13048,166 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on 5Ghz</t>
+        </is>
+      </c>
       <c r="C30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333983</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Sudharna Byanjankar</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 09:04:22 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 09:52:27 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 10:39:23 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>1h 35m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>12h 46m</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1333510</t>
+          <t>TKT1333983</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Kabiraj Limbu</t>
+          <t>Sudharna Byanjankar</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -12645,12 +13222,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -12660,44 +13237,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 09:04:22 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:24:32 PM</t>
+          <t>14 Sep 2026 09:52:27 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:55:56 AM</t>
+          <t>15 Sep 2026 10:39:23 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 35m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>21h 31m</t>
+          <t>12h 46m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1333787</t>
+          <t>TKT1333510</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ganesh bahadur dhakal</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -12732,17 +13309,17 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 05:06:15 PM</t>
+          <t>14 Sep 2026 01:24:32 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:51:57 AM</t>
+          <t>15 Sep 2026 10:55:56 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -12752,19 +13329,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>15h 45m</t>
+          <t>21h 31m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1334079</t>
+          <t>TKT1333787</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Bijaye Subedi</t>
+          <t>Ganesh bahadur dhakal</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -12794,22 +13371,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:17:25 AM</t>
+          <t>14 Sep 2026 05:06:15 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:06:08 AM</t>
+          <t>15 Sep 2026 08:51:57 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -12819,19 +13396,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2h 48m</t>
+          <t>15h 45m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1332693</t>
+          <t>TKT1334079</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Girish Ojha</t>
+          <t>Bijaye Subedi</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -12861,22 +13438,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>13 Sep 2026 04:22:39 PM</t>
+          <t>15 Sep 2026 08:17:25 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:28:00 AM</t>
+          <t>15 Sep 2026 11:06:08 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -12886,19 +13463,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 5m</t>
+          <t>2h 48m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1334100</t>
+          <t>TKT1332693</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Abisesh Giri 1</t>
+          <t>Girish Ojha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -12928,22 +13505,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : WIFI 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:05:49 AM</t>
+          <t>13 Sep 2026 04:22:39 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:22:50 AM</t>
+          <t>15 Sep 2026 11:28:00 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -12953,19 +13530,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2h 17m</t>
+          <t>1d 19h 5m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1334105</t>
+          <t>TKT1334100</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Abhisesh Giri</t>
+          <t>Abisesh Giri 1</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -13000,17 +13577,17 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:09:34 AM</t>
+          <t>15 Sep 2026 09:05:49 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:17:53 AM</t>
+          <t>15 Sep 2026 11:22:50 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -13020,29 +13597,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2h 8m</t>
+          <t>2h 17m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1334172</t>
+          <t>TKT1334105</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Dil Kumar Shrestha</t>
+          <t>Abhisesh Giri</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Blank TV Display</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13062,22 +13639,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:58:03 AM</t>
+          <t>15 Sep 2026 09:09:34 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:34:16 PM</t>
+          <t>15 Sep 2026 11:17:53 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -13087,29 +13664,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2h 36m</t>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1333648</t>
+          <t>TKT1334172</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Kushal Neupane</t>
+          <t>Dil Kumar Shrestha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -13129,22 +13706,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : IPTV blank display  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:17:35 PM</t>
+          <t>15 Sep 2026 09:58:03 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:47:26 AM</t>
+          <t>15 Sep 2026 12:34:16 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -13154,42 +13731,109 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>20h 29m</t>
+          <t>2h 36m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>TKT1333648</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Kushal Neupane</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Remote damage Issue</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 03:17:35 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 11:47:26 AM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>20h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>TKT1333455</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Ranjana jimee</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu
 (15 Sep 2026 01:31:35 PM) :
@@ -13205,113 +13849,46 @@
 Related Documents</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6 router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>14 Sep 2026 12:32:40 PM</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 01:31:34 PM</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t>1d 58m</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>TKT1333363</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Kanunalaya Inc. Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>14 Sep 2026 11:24:30 AM</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>15 Sep 2026 12:47:59 PM</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1334089</t>
+          <t>TKT1333363</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Arun Bhandari</t>
+          <t>Kanunalaya Inc. Pvt Ltd</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -13321,7 +13898,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -13341,22 +13918,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 08:40:37 AM</t>
+          <t>14 Sep 2026 11:24:30 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:27 PM</t>
+          <t>15 Sep 2026 12:47:59 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -13366,19 +13943,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>4h 5m</t>
+          <t>1d 1h 23m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1333526</t>
+          <t>TKT1334089</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Uttam KC</t>
+          <t>Arun Bhandari</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -13388,17 +13965,17 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -13408,44 +13985,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Dual band  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:36:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 01:34:08 PM</t>
+          <t>15 Sep 2026 08:40:37 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:21:58 PM</t>
+          <t>15 Sep 2026 12:46:27 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>23h 45m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>23h 47m</t>
+          <t>4h 5m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1333979</t>
+          <t>TKT1333526</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>lavkush kumar mukhiya</t>
+          <t>Uttam KC</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -13475,44 +14052,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : for wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:36:58 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 09:49:30 PM</t>
+          <t>14 Sep 2026 01:34:08 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:13:52 PM</t>
+          <t>15 Sep 2026 01:21:58 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 45m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>14h 24m</t>
+          <t>23h 47m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1333912</t>
+          <t>TKT1333979</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Saroj Karki</t>
+          <t>lavkush kumar mukhiya</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -13527,12 +14104,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -13542,44 +14119,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:56:46 PM</t>
+          <t>14 Sep 2026 09:49:30 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:27:57 PM</t>
+          <t>15 Sep 2026 12:13:52 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>14h 24m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>17h 31m</t>
+          <t>14h 24m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1334125</t>
+          <t>TKT1333912</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Niran Shahi Thakuri</t>
+          <t>Saroj Karki</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -13609,22 +14186,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:28:19 AM</t>
+          <t>14 Sep 2026 07:56:46 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:46:14 PM</t>
+          <t>15 Sep 2026 01:27:57 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -13634,19 +14211,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>3h 17m</t>
+          <t>17h 31m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1334129</t>
+          <t>TKT1334125</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Uday Bhahadur Rana Magar</t>
+          <t>Niran Shahi Thakuri</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -13661,12 +14238,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -13676,44 +14253,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:22:18 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:31:27 AM</t>
+          <t>15 Sep 2026 09:28:19 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:24:45 PM</t>
+          <t>15 Sep 2026 12:46:14 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1h 2m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>3h 53m</t>
+          <t>3h 17m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1334065</t>
+          <t>TKT1334129</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Saradha Panta</t>
+          <t>Uday Bhahadur Rana Magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -13728,12 +14305,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -13743,32 +14320,32 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 12:22:18 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 07:57:11 AM</t>
+          <t>15 Sep 2026 09:31:27 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:08:55 PM</t>
+          <t>15 Sep 2026 01:24:45 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 2m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>5h 11m</t>
+          <t>3h 53m</t>
         </is>
       </c>
     </row>
@@ -13909,12 +14486,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1333868</t>
+          <t>TKT1334065</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Ganesh Lal Gurung</t>
+          <t>Saradha Panta</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -13944,22 +14521,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>14 Sep 2026 07:06:45 PM</t>
+          <t>15 Sep 2026 07:57:11 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:01:58 PM</t>
+          <t>15 Sep 2026 01:08:55 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -13969,29 +14546,29 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>18h 55m</t>
+          <t>5h 11m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1333628</t>
+          <t>TKT1333868</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Biraj poudel</t>
+          <t>Ganesh Lal Gurung</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on 5Ghz</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14011,22 +14588,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Slow internet  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 02:59:37 PM</t>
+          <t>14 Sep 2026 07:06:45 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:26:43 PM</t>
+          <t>15 Sep 2026 02:01:58 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -14036,39 +14613,39 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>23h 27m</t>
+          <t>18h 55m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1334223</t>
+          <t>TKT1333628</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Srijana Magar</t>
+          <t>Biraj poudel</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on 5Ghz</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -14078,44 +14655,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>Case : Slow internet  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:39:14 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:26:08 AM</t>
+          <t>14 Sep 2026 02:59:37 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:50:45 PM</t>
+          <t>15 Sep 2026 02:26:43 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3h 24m</t>
+          <t>23h 27m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1333699</t>
+          <t>TKT1334223</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Lok Parsad Silwal</t>
+          <t>Srijana Magar</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -14145,44 +14722,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 01:39:14 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:49:03 PM</t>
+          <t>15 Sep 2026 10:26:08 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:17:52 PM</t>
+          <t>15 Sep 2026 01:50:45 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>11m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>22h 28m</t>
+          <t>3h 24m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1334316</t>
+          <t>TKT1333699</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Rama Shrestha</t>
+          <t>Lok Parsad Silwal</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -14212,44 +14789,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:15:01 AM</t>
+          <t>14 Sep 2026 03:49:03 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:57:47 PM</t>
+          <t>15 Sep 2026 02:17:52 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>22h 28m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2h 42m</t>
+          <t>22h 28m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1333643</t>
+          <t>TKT1334316</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Manish Agrawal</t>
+          <t>Rama Shrestha</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -14279,44 +14856,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>14 Sep 2026 03:15:17 PM</t>
+          <t>15 Sep 2026 11:15:01 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:46:25 PM</t>
+          <t>15 Sep 2026 01:57:47 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>2h 42m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>23h 31m</t>
+          <t>2h 42m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1334492</t>
+          <t>TKT1333643</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Dipak Kumar Karki</t>
+          <t>Manish Agrawal</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -14331,12 +14908,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -14346,54 +14923,54 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
+          <t>14 Sep 2026 03:15:17 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:43:35 PM</t>
+          <t>14 Sep 2026 03:15:17 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:47:15 PM</t>
+          <t>15 Sep 2026 02:46:25 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>23h 31m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2h 3m</t>
+          <t>23h 31m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1334031</t>
+          <t>TKT1334492</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Gautam shrestha</t>
+          <t>Dipak Kumar Karki</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -14413,22 +14990,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:01:53 PM</t>
+          <t>15 Sep 2026 02:47:15 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 06:10:23 AM</t>
+          <t>15 Sep 2026 12:43:35 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:01:53 PM</t>
+          <t>15 Sep 2026 02:47:15 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -14438,29 +15015,29 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>8h 51m</t>
+          <t>2h 3m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1334441</t>
+          <t>TKT1334031</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Sunshine Tradelink</t>
+          <t>Gautam shrestha</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -14480,22 +15057,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
+          <t>Case : Iptv issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:58:40 PM</t>
+          <t>15 Sep 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:14:10 PM</t>
+          <t>15 Sep 2026 06:10:23 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:58:40 PM</t>
+          <t>15 Sep 2026 03:01:53 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -14505,19 +15082,19 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>3h 44m</t>
+          <t>8h 51m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1334146</t>
+          <t>TKT1334441</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Ajib Shrestha</t>
+          <t>Sunshine Tradelink</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -14547,22 +15124,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:42 PM</t>
+          <t>15 Sep 2026 03:58:40 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 09:43:57 AM</t>
+          <t>15 Sep 2026 12:14:10 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:42 PM</t>
+          <t>15 Sep 2026 03:58:40 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -14572,19 +15149,19 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>6h 13m</t>
+          <t>3h 44m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1334656</t>
+          <t>TKT1334146</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Ashok Budal</t>
+          <t>Ajib Shrestha</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -14614,22 +15191,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:31 PM</t>
+          <t>15 Sep 2026 03:57:42 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 02:18:04 PM</t>
+          <t>15 Sep 2026 09:43:57 AM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:57:31 PM</t>
+          <t>15 Sep 2026 03:57:42 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -14639,29 +15216,29 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>6h 13m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1334472</t>
+          <t>TKT1334656</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Pramod Dhungel</t>
+          <t>Ashok Budal</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -14681,22 +15258,22 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:23:50 PM</t>
+          <t>15 Sep 2026 03:57:31 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 12:28:17 PM</t>
+          <t>15 Sep 2026 02:18:04 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:23:50 PM</t>
+          <t>15 Sep 2026 03:57:31 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
@@ -14706,39 +15283,39 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>2h 55m</t>
+          <t>1h 39m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1334285</t>
+          <t>TKT1334472</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Suman Darlami Magar</t>
+          <t>Pramod Dhungel</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -14748,32 +15325,32 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>Case : iptv setbox issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:53:46 AM</t>
+          <t>15 Sep 2026 03:23:50 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:53:46 AM</t>
+          <t>15 Sep 2026 12:28:17 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:48:09 PM</t>
+          <t>15 Sep 2026 03:23:50 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>4h 54m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>4h 54m</t>
+          <t>2h 55m</t>
         </is>
       </c>
     </row>
@@ -14847,12 +15424,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1334280</t>
+          <t>TKT1334285</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Gopal Prasad Dhakal</t>
+          <t>Suman Darlami Magar</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -14882,44 +15459,44 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:50:35 AM</t>
+          <t>15 Sep 2026 10:53:46 AM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 10:50:35 AM</t>
+          <t>15 Sep 2026 10:53:46 AM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:00:23 PM</t>
+          <t>15 Sep 2026 03:48:09 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>4h 9m</t>
+          <t>4h 54m</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>4h 9m</t>
+          <t>4h 54m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1334295</t>
+          <t>TKT1334280</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Amin Karki</t>
+          <t>Gopal Prasad Dhakal</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -14949,44 +15526,44 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:01:44 AM</t>
+          <t>15 Sep 2026 10:50:35 AM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 11:01:44 AM</t>
+          <t>15 Sep 2026 10:50:35 AM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:19:22 PM</t>
+          <t>15 Sep 2026 03:00:23 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>5h 17m</t>
+          <t>4h 9m</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>5h 17m</t>
+          <t>4h 9m</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TKT1334762</t>
+          <t>TKT1334295</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Junkeri ale Shrestha</t>
+          <t>Amin Karki</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -15001,12 +15578,12 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -15016,44 +15593,44 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wif 6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:58:24 PM</t>
+          <t>15 Sep 2026 11:01:44 AM</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:36:15 PM</t>
+          <t>15 Sep 2026 11:01:44 AM</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:58:24 PM</t>
+          <t>15 Sep 2026 04:19:22 PM</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 17m</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1h 22m</t>
+          <t>5h 17m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TKT1334529</t>
+          <t>TKT1334762</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Bhim Sen Thakuri</t>
+          <t>Junkeri ale Shrestha</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -15083,22 +15660,22 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:10:54 PM</t>
+          <t>15 Sep 2026 04:58:24 PM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:12:21 PM</t>
+          <t>15 Sep 2026 03:36:15 PM</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:10:54 PM</t>
+          <t>15 Sep 2026 04:58:24 PM</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
@@ -15108,19 +15685,19 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>3h 58m</t>
+          <t>1h 22m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>TKT1334791</t>
+          <t>TKT1334529</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>INDIRA RANABHAT</t>
+          <t>Bhim Sen Thakuri</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -15150,22 +15727,22 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:02:06 PM</t>
+          <t>15 Sep 2026 05:10:54 PM</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 03:52:57 PM</t>
+          <t>15 Sep 2026 01:12:21 PM</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:02:06 PM</t>
+          <t>15 Sep 2026 05:10:54 PM</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -15175,39 +15752,39 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1h 9m</t>
+          <t>3h 58m</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TKT1334532</t>
+          <t>TKT1334791</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Om parkash</t>
+          <t>INDIRA RANABHAT</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -15217,64 +15794,64 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:41:39 PM</t>
+          <t>15 Sep 2026 05:02:06 PM</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 01:12:54 PM</t>
+          <t>15 Sep 2026 03:52:57 PM</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:07:27 PM</t>
+          <t>15 Sep 2026 05:02:06 PM</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>3h 54m</t>
+          <t>1h 9m</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>TKT1334870</t>
+          <t>TKT1334532</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Raj KC</t>
+          <t>Om parkash</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -15284,32 +15861,32 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:44:50 PM</t>
+          <t>15 Sep 2026 04:41:39 PM</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 04:46:23 PM</t>
+          <t>15 Sep 2026 01:12:54 PM</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>15 Sep 2026 05:45:07 PM</t>
+          <t>15 Sep 2026 05:07:27 PM</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>25m</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>58m</t>
+          <t>3h 54m</t>
         </is>
       </c>
     </row>
@@ -15418,7 +15995,7 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -15450,67 +16027,335 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
+          <t>TKT1334870</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Raj KC</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 Router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:44:50 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 04:46:23 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 05:45:07 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>TKT1334286</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Yognath dhakal</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 06:15:02 PM</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 10:56:26 AM</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>15 Sep 2026 06:15:02 PM</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr">
         <is>
           <t>7h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>TKT1333865</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Dolma Lama</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>14 Sep 2026 07:05:43 PM</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:47:50 PM</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>23h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TKT1334260</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 03:58:58 PM</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 10:38:16 AM</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:43:27 PM</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW60"/>
+  <dimension ref="A1:AW61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12013,10 +12013,8 @@
           <t>Dolma Lama</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9818723103</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9818723103</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12102,10 +12100,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -12116,7 +12112,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -12212,10 +12208,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9709029533</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9709029533</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12250,10 +12244,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -12309,25 +12301,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDB226</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -12423,10 +12411,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9709029533</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9709029533</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12461,10 +12447,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -12520,50 +12504,253 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>CDB226</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>2h 44m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>8h 5m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
           <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS60" s="3" t="inlineStr">
-        <is>
-          <t>2h 44m</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>8h 5m</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV60" s="3" t="inlineStr">
-        <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 6:51 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334637</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Om Khadka</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Om Khadka</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9851082021</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>omkhadka_fttx</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:07:36 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.70292</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Battisputali,Hotel Miracle Rastriya Banijaya Bank, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr"/>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>04:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>L33-6</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.34114</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>4h 44m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -12615,7 +12802,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -12625,7 +12812,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -12636,7 +12823,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12835,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 26m</t>
+          <t>2h 23m</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12847,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9h 42m</t>
+          <t>9h 36m</t>
         </is>
       </c>
     </row>
@@ -12701,14 +12888,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -12845,14 +13032,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16378,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Case : sky com to net tv   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -16258,7 +16445,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -16325,14 +16512,14 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
           <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Case : ssid auto disconnect  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>15 Sep 2026 03:58:58 PM</t>
@@ -16356,6 +16543,73 @@
       <c r="M81" s="5" t="inlineStr">
         <is>
           <t>8h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>TKT1334637</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Om Khadka</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 02:07:36 PM</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 06:51:48 PM</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>4h 44m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_15_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_15_Sep_2026.xlsx
@@ -12614,10 +12614,8 @@
           <t>Om Khadka</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9851082021</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9851082021</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12652,10 +12650,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.70292</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.70292</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -12707,25 +12703,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>L33-6</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.34114</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.34114</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -16579,7 +16571,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
